--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
@@ -413,736 +413,959 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.14969</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.82378</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.95726</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.81943</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.85477</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.34956</v>
+        <v>17.06026</v>
       </c>
       <c r="D3" t="n">
-        <v>16.88082</v>
+        <v>16.61201</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0475</v>
+        <v>16.898</v>
       </c>
       <c r="F3" t="n">
-        <v>42.2624</v>
+        <v>43.55019</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0503</v>
+        <v>0.05068</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86742</v>
+        <v>1.82632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.07265</v>
+        <v>17.02344</v>
       </c>
       <c r="D4" t="n">
-        <v>16.79351</v>
+        <v>16.73436</v>
       </c>
       <c r="E4" t="n">
-        <v>17.08757</v>
+        <v>16.93873</v>
       </c>
       <c r="F4" t="n">
-        <v>43.43568</v>
+        <v>43.67971</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05186</v>
+        <v>0.05124</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86261</v>
+        <v>1.86381</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.01097</v>
+        <v>17.23184</v>
       </c>
       <c r="D5" t="n">
-        <v>16.87662</v>
+        <v>16.9461</v>
       </c>
       <c r="E5" t="n">
-        <v>17.15936</v>
+        <v>17.07052</v>
       </c>
       <c r="F5" t="n">
-        <v>43.04915</v>
+        <v>44.13269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05226</v>
+        <v>0.05145</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83674</v>
+        <v>1.81653</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.29198</v>
+        <v>17.40408</v>
       </c>
       <c r="D6" t="n">
-        <v>16.69948</v>
+        <v>16.62383</v>
       </c>
       <c r="E6" t="n">
-        <v>16.79788</v>
+        <v>17.02677</v>
       </c>
       <c r="F6" t="n">
-        <v>43.64168</v>
+        <v>41.26805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05209</v>
+        <v>0.05048</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83229</v>
+        <v>1.85766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.38656</v>
+        <v>17.12822</v>
       </c>
       <c r="D7" t="n">
-        <v>16.96975</v>
+        <v>16.80442</v>
       </c>
       <c r="E7" t="n">
-        <v>17.01698</v>
+        <v>16.89154</v>
       </c>
       <c r="F7" t="n">
-        <v>44.13662</v>
+        <v>44.28129</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05181</v>
+        <v>0.05185</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86776</v>
+        <v>1.84995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.16943</v>
+        <v>17.38595</v>
       </c>
       <c r="D8" t="n">
-        <v>16.63843</v>
+        <v>16.81213</v>
       </c>
       <c r="E8" t="n">
-        <v>16.76668</v>
+        <v>16.81694</v>
       </c>
       <c r="F8" t="n">
-        <v>43.21273</v>
+        <v>43.76549</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05159</v>
+        <v>0.05185</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84378</v>
+        <v>1.89884</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.10863</v>
+        <v>17.34147</v>
       </c>
       <c r="D9" t="n">
-        <v>16.6299</v>
+        <v>16.64838</v>
       </c>
       <c r="E9" t="n">
-        <v>17.03508</v>
+        <v>16.82462</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9264</v>
+        <v>42.64765</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05149</v>
+        <v>0.05153</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85314</v>
+        <v>1.85341</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.99457</v>
+        <v>17.25534</v>
       </c>
       <c r="D10" t="n">
-        <v>16.86573</v>
+        <v>16.96638</v>
       </c>
       <c r="E10" t="n">
-        <v>17.30755</v>
+        <v>17.00806</v>
       </c>
       <c r="F10" t="n">
-        <v>42.9096</v>
+        <v>42.81063</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05161</v>
+        <v>0.05225</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79857</v>
+        <v>1.85985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.31497</v>
+        <v>17.06772</v>
       </c>
       <c r="D11" t="n">
-        <v>16.74711</v>
+        <v>16.60769</v>
       </c>
       <c r="E11" t="n">
-        <v>16.81314</v>
+        <v>16.92088</v>
       </c>
       <c r="F11" t="n">
-        <v>43.11984</v>
+        <v>42.8936</v>
       </c>
       <c r="G11" t="n">
         <v>0.051</v>
       </c>
       <c r="H11" t="n">
-        <v>1.84794</v>
+        <v>1.84017</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.26749</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.63585</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.90446</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.79569</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.86993</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60673</v>
+        <v>17.21869</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10695</v>
+        <v>16.9854</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.19925</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44.00595</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.8542</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62221</v>
+        <v>16.98159</v>
       </c>
       <c r="D14" t="n">
-        <v>1.14535</v>
+        <v>16.63132</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.91639</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.46009</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.85373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.63239</v>
+        <v>17.00728</v>
       </c>
       <c r="D15" t="n">
-        <v>1.12169</v>
+        <v>16.76147</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.97218</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.79676</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05206</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62148</v>
+        <v>16.93045</v>
       </c>
       <c r="D16" t="n">
-        <v>1.14703</v>
+        <v>16.58692</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.89872</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.46119</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.83377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.63066</v>
+        <v>17.26904</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12425</v>
+        <v>16.83523</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.98811</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.78147</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.61536</v>
+        <v>17.36387</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13864</v>
+        <v>16.86666</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.91687</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.65807</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.80103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.61696</v>
+        <v>17.22018</v>
       </c>
       <c r="D19" t="n">
-        <v>1.14567</v>
+        <v>16.86754</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.89773</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44.60876</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.85524</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.61656</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.1544</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.61821</v>
+        <v>0.6129599999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1.11935</v>
+        <v>1.11725</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.61527</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.15129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.76654</v>
+        <v>0.61378</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08312</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.61005</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.96479</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11191</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09608</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12858</v>
+        <v>1.11838</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74843</v>
+        <v>0.62851</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08195</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.61361</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9922299999999999</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11193</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00779</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09223000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12823</v>
+        <v>1.14335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75746</v>
+        <v>0.62362</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08228000000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.62403</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.97464</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11176</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09512</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12683</v>
+        <v>1.13372</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.769</v>
+        <v>0.62437</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08196000000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.61625</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.98807</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11094</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00779</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09427000000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12513</v>
+        <v>1.13122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.76781</v>
+        <v>0.62243</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08283</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.61437</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9956700000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11183</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09427000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12685</v>
+        <v>1.1473</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75941</v>
+        <v>0.61312</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08119</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.61566</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.97764</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1112</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09308</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12624</v>
+        <v>1.14048</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76364</v>
+        <v>0.61549</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08282</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.60733</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.97424</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11093</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09378</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12765</v>
+        <v>1.13269</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.77512</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08211</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.62992</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.98672</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11204</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09383</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13095</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7722599999999999</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.62099</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.96735</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.11069</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09614</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12647</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7647699999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.61978</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.98826</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11291</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09488000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12692</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.75461</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08395</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.97199</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11113</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09285</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.13049</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.75206</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11041</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12638</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74874</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08022</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61427</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.97501</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11092</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09511</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.13042</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.76261</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08197</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.61112</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11079</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09686</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12818</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.75823</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08406</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61614</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.97382</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09418</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12777</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.76535</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08295</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.98048</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09433999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12772</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0.7642099999999999</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08147</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.62278</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.98198</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.11194</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09508999999999999</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.13037</v>
+      <c r="C39" t="n">
+        <v>0.74278</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08230999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.61879</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.98771</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10993</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0922</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.13271</v>
       </c>
     </row>
   </sheetData>
